--- a/workbooks/AML_Transaction_Monitoring_Practice.xlsx
+++ b/workbooks/AML_Transaction_Monitoring_Practice.xlsx
@@ -2,10 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="1" r:id="R55aed2444ec7475e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="2" r:id="R5167ccbcecc54b18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R6580d88b8d114059"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Log" sheetId="4" r:id="R4aeedb0906d74254"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="1" r:id="R9094f8f0e72b4b7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="2" r:id="R0feb8f2777ab45ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="Rbc32778410584cc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Log" sheetId="4" r:id="R2c34d8ad42a842f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLOOKUP Walkthrough" sheetId="5" r:id="R530d58bb23a74d21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pivot Summary Example" sheetId="6" r:id="R070a2c34cd8c47a9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,8 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="$#,##0.00"/>
+    <x:numFmt numFmtId="201" formatCode="$#,##0"/>
   </x:numFmts>
   <x:fonts count="2">
     <x:font>
@@ -31,7 +34,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -43,6 +46,11 @@
         <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF15324B"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -51,7 +59,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -66,6 +74,10 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -76,7 +88,7 @@
         <x:color rgb="FF8C4B00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0C2"/>
         </x:patternFill>
       </x:fill>
@@ -4451,7 +4463,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43b856ece11746a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R782f0bc126964b06"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4651,7 +4663,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0beb160b0fd74652"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5994b69170c540ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4838,4 +4850,954 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="19" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="80" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="19" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="27" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="50" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="12" t="str">
+        <x:v>Customer_ID</x:v>
+      </x:c>
+      <x:c r="B1" s="12" t="str">
+        <x:v>Customer_Name</x:v>
+      </x:c>
+      <x:c r="C1" s="12" t="str">
+        <x:v>Industry</x:v>
+      </x:c>
+      <x:c r="D1" s="12" t="str">
+        <x:v>Risk_Rating</x:v>
+      </x:c>
+      <x:c r="E1" s="12" t="str">
+        <x:v>Expected_Monthly_USD</x:v>
+      </x:c>
+      <x:c r="F1" s="12" t="str">
+        <x:v>Explanation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>C001</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:f>VLOOKUP(A2,Customers!$A$2:$F$9,2,FALSE)</x:f>
+        <x:v>Cedar Market</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:f>VLOOKUP(A2,Customers!$A$2:$F$9,3,FALSE)</x:f>
+        <x:v>Retail</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:f>VLOOKUP(A2,Customers!$A$2:$F$9,4,FALSE)</x:f>
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="E2" s="13" t="n">
+        <x:f>VLOOKUP(A2,Customers!$A$2:$F$9,6,FALSE)</x:f>
+        <x:v>5200</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>Exact-match lookup against Customers tab</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>C002</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:f>VLOOKUP(A3,Customers!$A$2:$F$9,2,FALSE)</x:f>
+        <x:v>Blue Heron Design</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:f>VLOOKUP(A3,Customers!$A$2:$F$9,3,FALSE)</x:f>
+        <x:v>Consulting</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:f>VLOOKUP(A3,Customers!$A$2:$F$9,4,FALSE)</x:f>
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="n">
+        <x:f>VLOOKUP(A3,Customers!$A$2:$F$9,6,FALSE)</x:f>
+        <x:v>3400</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>Exact-match lookup against Customers tab</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>C003</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:f>VLOOKUP(A4,Customers!$A$2:$F$9,2,FALSE)</x:f>
+        <x:v>Atlas Imports</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:f>VLOOKUP(A4,Customers!$A$2:$F$9,3,FALSE)</x:f>
+        <x:v>Import / Export</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:f>VLOOKUP(A4,Customers!$A$2:$F$9,4,FALSE)</x:f>
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E4" s="13" t="n">
+        <x:f>VLOOKUP(A4,Customers!$A$2:$F$9,6,FALSE)</x:f>
+        <x:v>9800</x:v>
+      </x:c>
+      <x:c r="F4" t="str">
+        <x:v>Exact-match lookup against Customers tab</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>C004</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:f>VLOOKUP(A5,Customers!$A$2:$F$9,2,FALSE)</x:f>
+        <x:v>Luna Cafe</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:f>VLOOKUP(A5,Customers!$A$2:$F$9,3,FALSE)</x:f>
+        <x:v>Restaurant</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:f>VLOOKUP(A5,Customers!$A$2:$F$9,4,FALSE)</x:f>
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="E5" s="13" t="n">
+        <x:f>VLOOKUP(A5,Customers!$A$2:$F$9,6,FALSE)</x:f>
+        <x:v>2800</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>Exact-match lookup against Customers tab</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>C005</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:f>VLOOKUP(A6,Customers!$A$2:$F$9,2,FALSE)</x:f>
+        <x:v>River Bend Services</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:f>VLOOKUP(A6,Customers!$A$2:$F$9,3,FALSE)</x:f>
+        <x:v>Services</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:f>VLOOKUP(A6,Customers!$A$2:$F$9,4,FALSE)</x:f>
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="E6" s="13" t="n">
+        <x:f>VLOOKUP(A6,Customers!$A$2:$F$9,6,FALSE)</x:f>
+        <x:v>4600</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>Exact-match lookup against Customers tab</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>C006</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:f>VLOOKUP(A7,Customers!$A$2:$F$9,2,FALSE)</x:f>
+        <x:v>Maple Books</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:f>VLOOKUP(A7,Customers!$A$2:$F$9,3,FALSE)</x:f>
+        <x:v>Retail</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:f>VLOOKUP(A7,Customers!$A$2:$F$9,4,FALSE)</x:f>
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="E7" s="13" t="n">
+        <x:f>VLOOKUP(A7,Customers!$A$2:$F$9,6,FALSE)</x:f>
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>Exact-match lookup against Customers tab</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>C007</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:f>VLOOKUP(A8,Customers!$A$2:$F$9,2,FALSE)</x:f>
+        <x:v>Summit Supplies</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:f>VLOOKUP(A8,Customers!$A$2:$F$9,3,FALSE)</x:f>
+        <x:v>Wholesale</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:f>VLOOKUP(A8,Customers!$A$2:$F$9,4,FALSE)</x:f>
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="E8" s="13" t="n">
+        <x:f>VLOOKUP(A8,Customers!$A$2:$F$9,6,FALSE)</x:f>
+        <x:v>6800</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>Exact-match lookup against Customers tab</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>C008</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:f>VLOOKUP(A9,Customers!$A$2:$F$9,2,FALSE)</x:f>
+        <x:v>Orchid Logistics</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:f>VLOOKUP(A9,Customers!$A$2:$F$9,3,FALSE)</x:f>
+        <x:v>Transportation</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:f>VLOOKUP(A9,Customers!$A$2:$F$9,4,FALSE)</x:f>
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="E9" s="13" t="n">
+        <x:f>VLOOKUP(A9,Customers!$A$2:$F$9,6,FALSE)</x:f>
+        <x:v>11500</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>Exact-match lookup against Customers tab</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="12" t="str">
+        <x:v>HOW TO PRACTICE</x:v>
+      </x:c>
+      <x:c r="B12" s="12" t="str">
+        <x:v>INSTRUCTIONS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Step 1</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Open Customers tab: ID is column A, risk rating is column D.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Step 2</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Select VLOOKUP Walkthrough!D2: =VLOOKUP(A2,Customers!$A$2:$F$9,4,FALSE)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Step 3</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>A2 is lookup value; Customers!$A$2:$F$9 is fixed lookup table; 4 returns risk; FALSE requires exact match.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Step 4</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Change A2 to C003; confirm the returned rating changes to High. Restore C001.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>Step 5</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>Try an unknown ID (C999); #N/A means no match. Restore C001.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>Step 6</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>Filter Transactions to C001 and compare activity to retrieved profile and expected activity.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="19" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="94" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="12" t="str">
+        <x:v>Customer ID</x:v>
+      </x:c>
+      <x:c r="B1" s="12" t="str">
+        <x:v>Transaction Type</x:v>
+      </x:c>
+      <x:c r="C1" s="12" t="str">
+        <x:v>Count</x:v>
+      </x:c>
+      <x:c r="D1" s="12" t="str">
+        <x:v>Total USD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>C001</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>ACH Credit</x:v>
+      </x:c>
+      <x:c r="C2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="n">
+        <x:v>6668.21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>C001</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>ACH Debit</x:v>
+      </x:c>
+      <x:c r="C3" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="n">
+        <x:v>3198.08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>C001</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Card Settlement</x:v>
+      </x:c>
+      <x:c r="C4" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D4" s="2" t="n">
+        <x:v>5929.89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>C001</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>Cash Deposit</x:v>
+      </x:c>
+      <x:c r="C5" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D5" s="2" t="n">
+        <x:v>49705.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>C001</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Domestic Wire</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D6" s="2" t="n">
+        <x:v>4721.57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>C002</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>ACH Credit</x:v>
+      </x:c>
+      <x:c r="C7" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="n">
+        <x:v>4494.42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>C002</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>ACH Debit</x:v>
+      </x:c>
+      <x:c r="C8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D8" s="2" t="n">
+        <x:v>4506.56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>C002</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>Card Settlement</x:v>
+      </x:c>
+      <x:c r="C9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D9" s="2" t="n">
+        <x:v>5770.17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>C002</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Cash Deposit</x:v>
+      </x:c>
+      <x:c r="C10" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="n">
+        <x:v>9471.68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>C002</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Domestic Wire</x:v>
+      </x:c>
+      <x:c r="C11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="n">
+        <x:v>6712.4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>C003</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>ACH Credit</x:v>
+      </x:c>
+      <x:c r="C12" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D12" s="2" t="n">
+        <x:v>9239.95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>C003</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>ACH Debit</x:v>
+      </x:c>
+      <x:c r="C13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D13" s="2" t="n">
+        <x:v>7191.26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>C003</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Card Settlement</x:v>
+      </x:c>
+      <x:c r="C14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D14" s="2" t="n">
+        <x:v>8847.77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>C003</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Cash Deposit</x:v>
+      </x:c>
+      <x:c r="C15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D15" s="2" t="n">
+        <x:v>3178.59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>C003</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Domestic Wire</x:v>
+      </x:c>
+      <x:c r="C16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D16" s="2" t="n">
+        <x:v>5961.22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>C003</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>International Wire</x:v>
+      </x:c>
+      <x:c r="C17" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D17" s="2" t="n">
+        <x:v>44750</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>C004</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>ACH Credit</x:v>
+      </x:c>
+      <x:c r="C18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D18" s="2" t="n">
+        <x:v>9802.08</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>C004</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>ACH Debit</x:v>
+      </x:c>
+      <x:c r="C19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D19" s="2" t="n">
+        <x:v>8281.64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>C004</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>Card Settlement</x:v>
+      </x:c>
+      <x:c r="C20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D20" s="2" t="n">
+        <x:v>8696.69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>C004</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>Cash Deposit</x:v>
+      </x:c>
+      <x:c r="C21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D21" s="2" t="n">
+        <x:v>5555.63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>C004</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>Domestic Wire</x:v>
+      </x:c>
+      <x:c r="C22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D22" s="2" t="n">
+        <x:v>4246.03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>C005</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>ACH Credit</x:v>
+      </x:c>
+      <x:c r="C23" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D23" s="2" t="n">
+        <x:v>9675.52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>C005</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>ACH Debit</x:v>
+      </x:c>
+      <x:c r="C24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D24" s="2" t="n">
+        <x:v>1724.52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>C005</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>Card Settlement</x:v>
+      </x:c>
+      <x:c r="C25" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D25" s="2" t="n">
+        <x:v>7367.91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>C005</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>Cash Deposit</x:v>
+      </x:c>
+      <x:c r="C26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D26" s="2" t="n">
+        <x:v>6287.21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>C005</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>Domestic Wire</x:v>
+      </x:c>
+      <x:c r="C27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D27" s="2" t="n">
+        <x:v>6329.85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>C006</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>ACH Credit</x:v>
+      </x:c>
+      <x:c r="C28" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D28" s="2" t="n">
+        <x:v>3073.93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>C006</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>ACH Debit</x:v>
+      </x:c>
+      <x:c r="C29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D29" s="2" t="n">
+        <x:v>8876.52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>C006</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>Card Settlement</x:v>
+      </x:c>
+      <x:c r="C30" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D30" s="2" t="n">
+        <x:v>10411.17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>C006</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>Cash Deposit</x:v>
+      </x:c>
+      <x:c r="C31" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D31" s="2" t="n">
+        <x:v>5253.12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>C006</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>Domestic Wire</x:v>
+      </x:c>
+      <x:c r="C32" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D32" s="2" t="n">
+        <x:v>3377.56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>C007</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>ACH Credit</x:v>
+      </x:c>
+      <x:c r="C33" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D33" s="2" t="n">
+        <x:v>7907.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>C007</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>ACH Debit</x:v>
+      </x:c>
+      <x:c r="C34" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D34" s="2" t="n">
+        <x:v>6537.42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>C007</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>Card Settlement</x:v>
+      </x:c>
+      <x:c r="C35" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D35" s="2" t="n">
+        <x:v>2052.43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>C007</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>Cash Deposit</x:v>
+      </x:c>
+      <x:c r="C36" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D36" s="2" t="n">
+        <x:v>3873.35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>C007</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>Domestic Wire</x:v>
+      </x:c>
+      <x:c r="C37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D37" s="2" t="n">
+        <x:v>7993.44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>C008</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>ACH Credit</x:v>
+      </x:c>
+      <x:c r="C38" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D38" s="2" t="n">
+        <x:v>1424.76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>C008</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>ACH Debit</x:v>
+      </x:c>
+      <x:c r="C39" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D39" s="2" t="n">
+        <x:v>7218.38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>C008</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>Card Settlement</x:v>
+      </x:c>
+      <x:c r="C40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D40" s="2" t="n">
+        <x:v>2424.75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>C008</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>Cash Deposit</x:v>
+      </x:c>
+      <x:c r="C41" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D41" s="2" t="n">
+        <x:v>6223.89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>C008</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>Domestic Wire</x:v>
+      </x:c>
+      <x:c r="C42" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D42" s="2" t="n">
+        <x:v>1787.13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="12" t="str">
+        <x:v>CREATE A REAL PIVOTTABLE</x:v>
+      </x:c>
+      <x:c r="B45" s="12" t="str"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>Open Transactions and select the full data range, including the header row.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>Go to Insert &gt; PivotTable &gt; New Worksheet.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>Drag Customer_ID to Rows; Type to Columns.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>Drag Transaction_ID to Values; choose Count.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>Drag Amount_USD to Values; choose Sum; format as Currency.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>Filter customer C001 and investigate flagged cluster on Aug 12–15.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="str">
+        <x:v>NOTE</x:v>
+      </x:c>
+      <x:c r="B52" t="str">
+        <x:v>The summary above is a reproducible aggregate, NOT an actual Excel PivotTable object. Follow steps to build one.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>